--- a/www/download/COUNTRY.IRL.WIOD13.xlsx
+++ b/www/download/COUNTRY.IRL.WIOD13.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>Irlanda</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,2523 +852,4084 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>0.791728047333354</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>0.793285656462526</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>0.83647008002156</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>0.890583022093105</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>0.938262390790355</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>1.08271976714892</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>1.11656986366326</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>1.05752964034084</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>0.884016998033016</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>0.803923180836867</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>0.80379392216222</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>0.796431997410537</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>0.729660720781679</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.679902076537751</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.716948691519964</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.285</t>
+          <t>0.206592529308739</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.331</t>
+          <t>0.199274034003765</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.405</t>
+          <t>0.350762159889287</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1.526</t>
+          <t>0.420342294244058</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1.622</t>
+          <t>0.419446604753622</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1.697</t>
+          <t>0.422686604597048</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1.748</t>
+          <t>0.267986825561934</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>1.779</t>
+          <t>0.205605649915494</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>1.814</t>
+          <t>0.338256256572875</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>1.871</t>
+          <t>0.426880367359821</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>1.962</t>
+          <t>0.252694098354357</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2.048</t>
+          <t>0.194091226916802</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>2.123</t>
+          <t>0.129239538082703</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2.177</t>
+          <t>0.124938327275531</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2.002</t>
+          <t>0.0534451854475124</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.018</t>
+          <t>0.622401951819617</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.063</t>
+          <t>0.590477662587837</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.122</t>
+          <t>0.822593503312852</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1.224</t>
+          <t>0.906388370632351</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1.311</t>
+          <t>0.88693950502242</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.381</t>
+          <t>0.888615523831315</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1.432</t>
+          <t>0.72190344480509</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>1.461</t>
+          <t>0.631800025148047</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>1.494</t>
+          <t>0.835922144292176</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>1.541</t>
+          <t>0.940405402043573</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>0.857272029022559</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>1.714</t>
+          <t>0.95257580797026</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>1.762</t>
+          <t>0.847609850337369</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>0.723999953552076</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>1.585</t>
+          <t>0.562456067410611</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2547.899</t>
+          <t>0.855734456474345</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2653.568</t>
+          <t>0.875338756698846</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2769.255</t>
+          <t>1.20926343718533</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2978.043</t>
+          <t>1.36097157441748</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>3146.232</t>
+          <t>1.37631708400356</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>3278.661</t>
+          <t>1.42513433090122</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3360.912</t>
+          <t>1.23146595471258</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3387.924</t>
+          <t>1.12880334307916</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>3426.525</t>
+          <t>1.3475213469964</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>3525.15</t>
+          <t>1.49275993510822</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>3696.057</t>
+          <t>1.15700961555074</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>3837.868</t>
+          <t>1.4277685414545</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>3943.674</t>
+          <t>1.03740287416005</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>3993.21</t>
+          <t>0.94276583940359</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>3609.214</t>
+          <t>0.759837912799122</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1929.917</t>
+          <t>4450540427.85295</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2034.51</t>
+          <t>4554955163.99926</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2130.014</t>
+          <t>4440092713.81733</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2308.418</t>
+          <t>4405027251.75401</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2458.008</t>
+          <t>4917665026.74242</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2578.571</t>
+          <t>5140790014.19644</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2667.309</t>
+          <t>5247972966.48984</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2691.109</t>
+          <t>4965444559.59043</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2729.001</t>
+          <t>5288551828.73564</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2809.265</t>
+          <t>5799581353.2447</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2977.279</t>
+          <t>6098995468.97807</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>3109.725</t>
+          <t>6350663793.58705</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>3164.381</t>
+          <t>6634972648.73625</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>3056.794</t>
+          <t>5784508304.82427</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2739.318</t>
+          <t>5088881086.32051</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>22.86</t>
+          <t>1235060164.55085</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>24.37</t>
+          <t>1321019544.53951</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>24.99</t>
+          <t>1205556642.54143</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>26.39</t>
+          <t>1243310651.90305</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>27.65</t>
+          <t>1332243628.4394</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>28.42</t>
+          <t>1390219696.99494</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>29.28</t>
+          <t>1591651611.15825</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>31.05</t>
+          <t>1709894997.59156</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>33.1</t>
+          <t>1568941181.00444</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>34.89</t>
+          <t>1530477491.213</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>36.56</t>
+          <t>1803508630.20746</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>40.99</t>
+          <t>1866186237.70102</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>41.01</t>
+          <t>2070004207.98799</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>42.42</t>
+          <t>2096221701.63602</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>45.29</t>
+          <t>2076878749.15174</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>42.1</t>
+          <t>1176402.51599648</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>43.78</t>
+          <t>1116418.62599623</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>44.99</t>
+          <t>1040794.9912629</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>44.88</t>
+          <t>1011697.74055687</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>1051436.57231408</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>44.31</t>
+          <t>1083676.66739158</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>43.42</t>
+          <t>1046951.16770044</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>42.98</t>
+          <t>929509.061000326</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>42.16</t>
+          <t>770351.846906812</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>40.79</t>
+          <t>713386.703744335</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>38.68</t>
+          <t>682891.516163814</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>37.82</t>
+          <t>621548.028134913</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>37.03</t>
+          <t>580512.22264715</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>36.3</t>
+          <t>525000.66253043</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>35.84</t>
+          <t>578085.361509632</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>35.05</t>
+          <t>11537.5458063279</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>31.85</t>
+          <t>12008.3711910982</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>30.02</t>
+          <t>12342.3933136236</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>28.73</t>
+          <t>12834.3002078146</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>27.65</t>
+          <t>13738.3458422826</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>27.27</t>
+          <t>14808.8435180132</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>27.3</t>
+          <t>14820.3215255166</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>25.97</t>
+          <t>15106.2126433601</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>24.74</t>
+          <t>16425.3586868055</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>24.33</t>
+          <t>18569.3477077424</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>24.76</t>
+          <t>20755.2790394425</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>21.19</t>
+          <t>22827.8638830007</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>21.96</t>
+          <t>26218.7660346021</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>21.28</t>
+          <t>29278.1849674705</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>18.87</t>
+          <t>24829.9527076314</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>18.96</t>
+          <t>34648.6724990571</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>20.14</t>
+          <t>35725.2186789691</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>20.56</t>
+          <t>34600.6924241979</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>21.52</t>
+          <t>34139.1297923403</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>22.43</t>
+          <t>38939.6680888424</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>22.89</t>
+          <t>42353.7779613867</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>23.46</t>
+          <t>42103.8595239261</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>25.19</t>
+          <t>40725.9569198131</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>26.86</t>
+          <t>46722.7445668636</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>28.73</t>
+          <t>56466.4070068507</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>29.48</t>
+          <t>63597.4617780962</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>31.03</t>
+          <t>69404.4573966809</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>32.4</t>
+          <t>82032.3033229718</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>33.9</t>
+          <t>79177.8868355544</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>36.67</t>
+          <t>64974.3237033251</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>43.33</t>
+          <t>0.562609825007483</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>44.49</t>
+          <t>0.540105790048686</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>45.24</t>
+          <t>0.766830380641449</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>44.73</t>
+          <t>0.856670358253426</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>44.27</t>
+          <t>0.84501391030745</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>43.69</t>
+          <t>0.854793918955996</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>42.76</t>
+          <t>0.675812192162211</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>42.45</t>
+          <t>0.573844390239182</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>42.2</t>
+          <t>0.739390095256908</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>40.92</t>
+          <t>0.83554806769672</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>0.650825764633821</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>41.04</t>
+          <t>0.666353020468547</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>41.06</t>
+          <t>0.528683441016161</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>40.52</t>
+          <t>0.458239710083075</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>40.14</t>
+          <t>0.318958963639641</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>37.71</t>
+          <t>10488.7768743871</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>35.37</t>
+          <t>11033.4416769794</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>34.2</t>
+          <t>11134.4807396276</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>33.75</t>
+          <t>11315.3345769877</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>33.3</t>
+          <t>13376.253101754</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>33.42</t>
+          <t>10874.2771560101</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>33.78</t>
+          <t>10630.7815635772</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>32.36</t>
+          <t>11640.9397715973</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>30.94</t>
+          <t>14520.5981117085</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>30.35</t>
+          <t>16629.150595242</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>29.37</t>
+          <t>18821.3137148451</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>27.93</t>
+          <t>21025.8767361749</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>26.54</t>
+          <t>27046.9606938446</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>25.58</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>23.19</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.791728047333354</t>
+          <t>1213.69416662808</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.793285656462526</t>
+          <t>1242.40507694314</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.83647008002156</t>
+          <t>1074.37374800829</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.890583022093105</t>
+          <t>1015.90864491634</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.938262390790355</t>
+          <t>1016.51353302642</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.08271976714892</t>
+          <t>1006.4313748787</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.11656986366326</t>
+          <t>1111.7160223134</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.05752964034084</t>
+          <t>1170.22637920096</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.884016998033016</t>
+          <t>1050.02098142146</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.803923180836867</t>
+          <t>993.043397519071</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.80379392216222</t>
+          <t>1106.59976389837</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.796431997410537</t>
+          <t>1088.82123100428</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.729660720781679</t>
+          <t>1174.8857655716</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.679902076537751</t>
+          <t>1211.74207747625</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.716948691519964</t>
+          <t>1310.35674393727</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>2097820378.53812</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>2329955942.71713</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>2406789623.51648</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>2669858297.20549</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>3436343548.01625</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>3576663781.56935</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>4365119255.05504</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>5310330348.08393</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>5770804954.25832</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>5951687202.76055</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.082</t>
+          <t>5633579681.79038</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>5228013875.52325</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.108</t>
+          <t>5544112463.22339</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>5044952058.73946</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.107</t>
+          <t>5858370103.23178</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>2793831350.64625</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>3121662360.57753</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>3198485767.53089</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>4000214862.6715</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>5025376766.04128</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>5436804005.96271</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>6215838007.89562</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>7460905267.98536</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.074</t>
+          <t>7844023525.75965</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>7892285256.40625</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>7198139126.80324</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>6425847349.61643</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>6117175467.45968</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.148</t>
+          <t>5896795579.09819</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>6754078910.44794</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.166</t>
+          <t>-696010972.10813</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.178</t>
+          <t>-791706417.860399</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.182</t>
+          <t>-791696144.014403</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.185</t>
+          <t>-1330356565.46602</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.187</t>
+          <t>-1589033218.02503</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.178</t>
+          <t>-1860140224.39337</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.184</t>
+          <t>-1850718752.84058</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.207</t>
+          <t>-2150574919.90143</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.272</t>
+          <t>-2073218571.50133</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.329</t>
+          <t>-1940598053.6457</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.371</t>
+          <t>-1564559445.01286</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.436</t>
+          <t>-1197833474.09318</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>-573063004.236293</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-851843520.358729</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-895708807.216162</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>1896.5304293273</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>1913.43525258601</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.165</t>
+          <t>1898.23617814467</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.178</t>
+          <t>1886.20746770957</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.195</t>
+          <t>1875.48160844953</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.206</t>
+          <t>1866.72279397154</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.225</t>
+          <t>1863.02726441487</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.249</t>
+          <t>1841.75422221535</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.319</t>
+          <t>1826.39609489643</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>1822.77888945512</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.417</t>
+          <t>1826.80340138113</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.464</t>
+          <t>1814.36054703426</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.551</t>
+          <t>1796.02841491489</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.562</t>
+          <t>1767.01041575443</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.482</t>
+          <t>1728.30677298171</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>1982.57565597468</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>1993.42090652609</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>1970.3144933982</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>1951.23602116876</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>1940.14272515808</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>1931.9719580468</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.094</t>
+          <t>1922.66108839587</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>1904.15739115956</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>1888.42301198405</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>1884.49634427102</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.177</t>
+          <t>1883.46088498513</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.195</t>
+          <t>1874.32421947824</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.228</t>
+          <t>1857.59312446018</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.235</t>
+          <t>1834.39292932134</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.202</t>
+          <t>1803.09834393462</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>20.62</t>
+          <t>47267.1435503917</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>19.91</t>
+          <t>52335.3517922755</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>35.06</t>
+          <t>58755.980409501</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>42.03</t>
+          <t>67689.9588631831</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>44.05</t>
+          <t>79579.0265480544</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>42.25</t>
+          <t>88633.6395201882</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>26.78</t>
+          <t>96846.7936380043</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>20.54</t>
+          <t>104885.773008976</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>33.81</t>
+          <t>125481.444754296</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>42.69</t>
+          <t>149748.221083719</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>25.26</t>
+          <t>159911.93169149</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>170932.367972707</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>12.91</t>
+          <t>202338.860603665</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>12.49</t>
+          <t>213772.943765359</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>195689.115276211</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>62.19</t>
+          <t>1836022651.0532</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>59.02</t>
+          <t>1785577971.4514</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>82.24</t>
+          <t>1696218136.29145</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>90.63</t>
+          <t>1641889662.45462</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>91.49</t>
+          <t>1987261826.30918</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>88.83</t>
+          <t>2121844158.26339</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>72.16</t>
+          <t>2063545072.64359</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>63.16</t>
+          <t>1855413285.98678</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>83.57</t>
+          <t>1963202032.86339</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>94.04</t>
+          <t>2318403922.77327</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>85.71</t>
+          <t>2335888792.89343</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>95.25</t>
+          <t>2247964095.50652</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>84.73</t>
+          <t>2318537510.74367</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>72.39</t>
+          <t>1988065904.62963</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>56.24</t>
+          <t>1654588052.41885</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>85.51</t>
+          <t>37802.9525057756</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>41997.3925849796</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>120.9</t>
+          <t>46212.1216525593</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>136.09</t>
+          <t>55125.4373668695</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>141.15</t>
+          <t>63494.400704881</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>142.47</t>
+          <t>72614.740911448</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>123.11</t>
+          <t>77624.1208204714</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>112.85</t>
+          <t>80475.6649472791</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>134.73</t>
+          <t>96366.1927540968</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>149.27</t>
+          <t>117771.706854291</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>115.68</t>
+          <t>131133.924261323</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>142.77</t>
+          <t>143958.75462874</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>103.71</t>
+          <t>171829.484913713</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>94.27</t>
+          <t>181990.362949974</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>75.98</t>
+          <t>154971.787825277</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2547.899</t>
+          <t>2472588064.11184</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2653.568</t>
+          <t>2583287943.30249</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2769.255</t>
+          <t>2386484203.92589</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2978.043</t>
+          <t>2501734814.53437</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>3146.232</t>
+          <t>3004628480.79288</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>3278.661</t>
+          <t>3320534058.2026</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>3360.912</t>
+          <t>3428434400.3319</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>3387.924</t>
+          <t>3398630002.52074</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>3426.525</t>
+          <t>3494342478.20439</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>3525.15</t>
+          <t>3999935652.36325</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>3696.057</t>
+          <t>4407426545.05076</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>3837.868</t>
+          <t>4430530383.69355</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>3943.674</t>
+          <t>4825937815.22624</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>3993.21</t>
+          <t>4232888087.28803</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>3609.214</t>
+          <t>3568250402.22218</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1929.917</t>
+          <t>9464.19104461608</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2034.51</t>
+          <t>10337.9592072959</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2130.014</t>
+          <t>12543.8587569417</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2308.418</t>
+          <t>12564.5214963136</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2458.008</t>
+          <t>16084.6258431734</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2578.571</t>
+          <t>16018.8986087402</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2667.309</t>
+          <t>19222.6728175329</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2691.109</t>
+          <t>24410.1080616971</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2729.001</t>
+          <t>29115.2520001989</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2809.265</t>
+          <t>31976.5142294279</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2977.279</t>
+          <t>28778.0074301669</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>3109.725</t>
+          <t>26973.6133439669</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>3164.381</t>
+          <t>30509.3756899523</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>3056.794</t>
+          <t>31782.5808153854</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2739.318</t>
+          <t>40717.3274509348</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>4452.551</t>
+          <t>-636565413.058634</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>4556.169</t>
+          <t>-797709971.85109</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>4440.938</t>
+          <t>-690266067.634437</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>4405.043</t>
+          <t>-859845152.07975</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>4839.926</t>
+          <t>-1017366654.4837</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>5141.846</t>
+          <t>-1198689899.9392</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>5249.747</t>
+          <t>-1364889327.68831</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>4967.22</t>
+          <t>-1543216716.53395</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>5289.275</t>
+          <t>-1531140445.341</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>5800.425</t>
+          <t>-1681531729.58999</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>6100.02</t>
+          <t>-2071537752.15733</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>6350.985</t>
+          <t>-2182566288.18703</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>6637.688</t>
+          <t>-2507400304.48257</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>5785.121</t>
+          <t>-2244822182.6584</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>5089.062</t>
+          <t>-1913662349.80333</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>35628.71028</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>38229.90603</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>41540.18573</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>46418.20626</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>50019.52065</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>48963.72501</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>52428.545</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>61114.62804</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>74132.09013</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>84365.43219</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>87903.43056</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>95997.10793</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.082</t>
+          <t>110084.02041</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>111640.89857</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>99658.50712</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1481.971</t>
+          <t>0.0731373909114822</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1531.064</t>
+          <t>0.0835955514040069</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1583.823</t>
+          <t>0.10230822034472</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1656.031</t>
+          <t>0.12550242077478</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>1735.007</t>
+          <t>0.132121678297524</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>1797.458</t>
+          <t>0.15968309150013</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1847.257</t>
+          <t>0.177128950674446</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>1841.8</t>
+          <t>0.196838389718304</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>1859.188</t>
+          <t>0.190328011787522</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>1907.23</t>
+          <t>0.177187131442162</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>1990.431</t>
+          <t>0.16072552823295</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>2088.801</t>
+          <t>0.150775716744177</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>2120.638</t>
+          <t>0.12853581338896</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2138.98</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>1944.717</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>30216.7274515467</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>32858.690471087</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>34730.506188777</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>36928.6783913506</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>39231.0631348185</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>38677.4118061508</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>41788.0281601937</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>47294.7074669603</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>61157.1850026985</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>73200.7446860464</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>82179.909290841</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>91298.543601515</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>107930.941673357</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>123709.969852541</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>106941.324329402</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1235.452</t>
+          <t>37408.3853721165</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1321.241</t>
+          <t>40364.5939571423</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1205.704</t>
+          <t>42672.3483138855</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>1243.342</t>
+          <t>45441.7179008546</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>1312.784</t>
+          <t>48009.4451438283</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>1390.447</t>
+          <t>47248.0235749582</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1591.902</t>
+          <t>50629.6601011787</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>1710.152</t>
+          <t>57285.7035400332</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>1569.116</t>
+          <t>73950.0882721045</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>1530.49</t>
+          <t>88451.5230381879</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>1803.652</t>
+          <t>98405.7780784118</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>1866.26</t>
+          <t>108777.262988193</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>2070.34</t>
+          <t>130100.676925427</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>2096.342</t>
+          <t>148319.207223746</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>2076.953</t>
+          <t>127815.480017101</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>56.21</t>
+          <t>165791.087053843</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>53.98</t>
+          <t>178033.329237241</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>76.66</t>
+          <t>181733.881635705</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>85.66</t>
+          <t>185067.896370213</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>87.24</t>
+          <t>186982.497140142</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>85.45</t>
+          <t>177753.198114959</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>67.55</t>
+          <t>184456.723820911</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>57.36</t>
+          <t>207323.147820766</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>73.92</t>
+          <t>272207.674054964</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>83.55</t>
+          <t>329071.438269788</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>65.07</t>
+          <t>370978.698109013</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>66.63</t>
+          <t>435573.725423319</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>52.84</t>
+          <t>549546.964525575</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>45.82</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>31.89</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1.177</t>
+          <t>37408.3853721165</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.117</t>
+          <t>39586.9000935393</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.041</t>
+          <t>42636.3199305665</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1.012</t>
+          <t>44339.1547181014</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>1.033</t>
+          <t>47127.5998055457</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>1.084</t>
+          <t>48888.9411973636</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1.047</t>
+          <t>50252.7586167629</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>51375.7154083659</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>52545.289767832</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0.713</t>
+          <t>55553.730422125</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>0.683</t>
+          <t>58875.9240749664</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>0.622</t>
+          <t>61543.1947969549</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>0.581</t>
+          <t>67220.7681768881</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>0.525</t>
+          <t>73453.1812739769</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>0.578</t>
+          <t>71293.6854282151</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>30216.7274515467</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>31981.71564716</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>34132.6468725914</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>35349.3904568689</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>37589.0812415935</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>39094.8874637977</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>40432.839510253</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>41172.2473951654</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>42185.0981845677</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>44788.0933941631</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>48212.8678112792</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>50722.3678438831</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>54977.3136530097</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>59860.5071632062</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>56684.3282598564</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>22614.3044178835</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>25916.2360028577</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>29727.3507461145</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>34541.8035791454</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>38080.6944361717</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>39258.4573550418</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>43303.4074988213</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>52450.0943399668</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>66329.3435078955</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>74936.3747818121</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>78447.0609315882</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>86699.8173818071</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>97683.4267745733</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>86698.7595662541</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>74385.0519628989</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>1929917147.60251</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2034509849.31277</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>2130014101.6263</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2308418033.48914</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2458008026.38916</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>2578571039.99907</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2667309175.65362</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>2691108649.85751</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>2729000750.27981</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>2809265001.64934</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>2977278513.48593</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>3109725073.94992</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>3164381155.58501</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>3056793726.46356</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>2739317842.58637</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2547899286.28545</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2653568154.19399</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>2769255347.01174</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2978042757.53249</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>3146232450.2526</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>3278660739.29116</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>3360911560.89258</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>3387924434.28586</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>3426524671.01494</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>3525150168.57143</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>3696056554.17269</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>3837868146.12786</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>3943673918.4152</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>3993210073.6081</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>3609213724.27385</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1481970602.21181</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>1531063892.41817</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>1583822946.40331</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>1656030558.37997</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>1735006644.63146</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>1797458421.50389</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1847256940.33823</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>1841799850.98145</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>1859187886.45714</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>1907230305.88212</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>1990430895.82127</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>2088800836.20737</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>2120637705.83515</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>2138979844.79252</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>1944717074.47156</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>1285146.05664965</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>1331163</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>1405489</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>1526234</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>1621650</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>1697054</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1748052</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>1779225</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>1814490</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>1870606</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>1962375</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>2047601</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>2123002</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>2176856.4465005</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>2001673.25116501</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>1017604.10366158</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>1063276.0353731</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>1122101.73114926</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>1223841</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>1310600.97593877</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>1381335.80857661</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1431707</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>1461166</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>1494199.83863608</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>1541199</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>1629775</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>1713951</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>1761877</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>1729924</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>1584972</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2547899286.28545</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2653568154.19399</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>2769255347.01174</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2978042757.53249</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>3146232450.2526</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>3278660739.29116</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>3360911560.89258</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>3387924434.28586</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>3426524671.01494</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>3525150168.57143</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>3696056554.17269</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>3837868146.12786</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>3943673918.4152</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>3993210073.6081</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>3609213724.27385</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>1929917147.60251</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2034509849.31277</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>2130014101.6263</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2308418033.48914</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2458008026.38916</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>2578571039.99907</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2667309175.65362</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>2691108649.85751</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>2729000750.27981</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>2809265001.64934</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>2977278513.48593</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>3109725073.94992</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>3164381155.58501</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>3056793726.46356</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>2739317842.58637</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.228551949077892</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.243723137843603</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.249858280534478</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.263939145793767</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.276483269509155</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.28420368499428</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.292821454861932</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.310523354271164</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.331000979590364</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.348869083619875</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0.365645356771562</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0.409887125460397</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0.41008319108744</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0.42418374560626</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0.452934382739975</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.420987678638385</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.437758976405333</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.449934012124202</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.448791732503489</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.446990165169487</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.443127372849649</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.434154610173299</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.429782298577874</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.421636914152267</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.407857989703823</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0.38679683229293</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0.378179481889638</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.370278519530993</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0.362968876895351</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0.358388550232721</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.350460372283722</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.318517885751064</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.300207707341319</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.287269121702744</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.276526565321358</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.272668942156071</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.273023934964769</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.259694347150962</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.247362106257369</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.243272926676302</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.247557810935509</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.211933392649964</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.219638289381567</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0.212847377498389</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0.188677067027303</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.189554344070667</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.201418712090427</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.205601942560401</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.2151627525334</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.224272432322089</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.228917850140343</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.234596609399241</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.251870921354052</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.268609409539807</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.287257104030716</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0.294773786798651</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0.310305463091801</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.323984639496917</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0.338950725981488</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0.366725580736755</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.433327810946452</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.44490994834356</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.452400829696932</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.447331669379548</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.4427128045549</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.436900933409306</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.427572595839524</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.424523639477111</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.422019268911282</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0.409196985907454</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0.411506251883783</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0.410382874176191</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0.410621569332512</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>0.405243912708142</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0.401421265114714</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.377117844982881</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.353671339566012</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.341997227742667</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.337505578087051</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.333014763123011</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.334181216450352</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.337830794761235</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.323605439168837</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.309371321548911</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.303545910061829</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>0.293719961317566</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0.279311662732008</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0.265393791170571</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0.25580536131037</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>0.231853154148531</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>134723.39307</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>149876.90979</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>164938.59555</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>178120.27518</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>195301.38045</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>206241.77683</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>224824.28026</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>249407.63682</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>318780.68156</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>379865.20657</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>417431.60801</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>463706.59768</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>550941.06294</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>561762.81601</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>482054.72113</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>60022.68979</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>66280.82996</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>72399.69906</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>79983.52148</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>86090.13958</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>86506.48093</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>93933.0676</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>109735.79788</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>140279.43178</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>163387.89782</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>176852.83901</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>195477.08037</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>227784.1037</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>235017.96679</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>202200.53198</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>131261.45336144</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>136759.567012045</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>144311.489342752</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>154908.383914814</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>169219.619632582</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>186069.652263705</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>203826.797026311</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>223182.255285232</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>244092.347013215</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>268622.229508064</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>299043.02653643</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>329852.481077754</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>361935.230409352</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -3374,7 +4940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,36 +4963,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3438,331 +5019,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3799,6 +5744,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>WIOD13</t>
